--- a/output/2026-09-05_22_Slovenia_Pomurska_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-05_22_Slovenia_Pomurska_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -464,7 +464,6 @@
           <t>VARGAL, prodaja in servis varilne opreme d.o.o.</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>Lendava</t>
@@ -522,10 +521,9 @@
           <t>(02) 537 13 13</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rivenditore di utensili elettrici (Bosch, Makita, Dewalt, Milwaukee, AEG) e materiale per falegnami/hobbisti. Attivita' orientata principalmente a falegnameria/hobbistica, ma vende anche utensileria elettrica generica (smerigliatrici, trapani) utilizzabile in metalworking. Indirizzo confermato: Obrtna ulica 24, 9000 Murska Sobota. Verificata su itis.siol.net, abprodukt.si.</t>
+          <t>Rivenditore di utensili elettrici (Bosch, Makita, Dewalt, Milwaukee, AEG) e materiale per falegnami/hobbisti. Attivita' orientata principalmente a falegnameria/hobbistica, ma vende anche utensileria elettrica generica (smerigliatrici, trapani) utilizzabile in metalworking. Indirizzo confermato: Obrtna ulica 24, 9000 Murska Sobota. Verificata su itis.siol.net, abprodukt.si. [DUPLICATO — vedi anche: 2026-09-05_21_Slovenia_Pomurska_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -540,7 +538,6 @@
           <t>CDC d.o.o.</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>Murska Sobota</t>
@@ -605,7 +602,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rivenditore e centro assistenza utensili elettrici Bosch, Makita, Dewalt, Milwaukee, Black&amp;Decker, AEG. Attiva dal 1992. Indirizzo: Cankarjeva 23, 9000 Murska Sobota. Verificata su Bizi.si e ricerca web.</t>
+          <t>Rivenditore e centro assistenza utensili elettrici Bosch, Makita, Dewalt, Milwaukee, Black&amp;Decker, AEG. Attiva dal 1992. Indirizzo: Cankarjeva 23, 9000 Murska Sobota. Verificata su Bizi.si e ricerca web. [DUPLICATO — vedi anche: 2026-09-05_21_Slovenia_Pomurska_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
